--- a/addons/TinyTools/ConfigGenerator/EquipConfig.xlsx
+++ b/addons/TinyTools/ConfigGenerator/EquipConfig.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,26 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,17 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,207 +413,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Rarity</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>BaseATK</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>BaseHP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>BaseSPD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>SetId</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>DropWeight</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>EquipSlot</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Rarity</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>装备ID</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>装备名</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>栏位</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>稀有度</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>基础攻击加成</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>基础生命加成</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>基础速度加成</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>套装ID(0=散件)</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>同稀有度掉落权重</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>栏位/稀有度/基础属性/套装归属。散件 SetId=0；套装件同稀有度数值 ×0.92 换套装效果</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>唯一</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>中文名</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1武器/2护甲/3饰品/4靴子</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1白/2绿/3蓝/4紫/5橙</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>加到基础攻击(加算)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>加到基础生命(加算)</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>加到基础速度(加算)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>P1套装用,本轮填0</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>越大越易掉</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -674,20 +565,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>精钢剑</t>
+          <t>布衣</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -705,23 +596,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>寒锋剑</t>
+          <t>木牌</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -736,23 +627,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>玄铁剑</t>
+          <t>草鞋</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -767,17 +658,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>龙泉剑</t>
+          <t>精钢剑</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -798,20 +689,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>布衣</t>
+          <t>皮甲</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -829,23 +720,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>皮甲</t>
+          <t>铜佩</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -860,23 +751,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>锁子甲</t>
+          <t>布靴</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -891,20 +782,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>玄铁甲</t>
+          <t>寒锋剑</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -922,20 +813,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>金鳞甲</t>
+          <t>锁子甲</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>960</v>
+        <v>240</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -953,23 +844,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>木牌</t>
+          <t>玉坠</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -984,23 +875,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>铜佩</t>
+          <t>皮靴</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1015,23 +906,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>玉坠</t>
+          <t>玄铁剑</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F17" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1046,23 +937,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>羊脂玉</t>
+          <t>玄铁甲</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="G18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1077,23 +968,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>龙纹玉</t>
+          <t>羊脂玉</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="G19" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1108,14 +999,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>草鞋</t>
+          <t>踏云靴</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1124,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1139,23 +1030,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>布靴</t>
+          <t>龙泉剑</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1170,23 +1061,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>皮靴</t>
+          <t>金鳞甲</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1201,23 +1092,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>踏云靴</t>
+          <t>龙纹玉</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1254,6 +1145,750 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>疾风刃</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>疾风衣</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>110</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>疾风符</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>55</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>疾风履</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>玄武锋</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>玄武铠</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>110</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>玄武印</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>55</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>玄武踞</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>破军枪</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>15</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>破军甲</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>221</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>破军令</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>110</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>破军靴</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>千机弩</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>15</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>千机衫</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>221</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>千机匣</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7</v>
+      </c>
+      <c r="F39" t="n">
+        <v>110</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4</v>
+      </c>
+      <c r="I39" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>千机履</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>7</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4</v>
+      </c>
+      <c r="I40" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>降龙剑</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>29</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>降龙袍</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>442</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>降龙珠</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" t="n">
+        <v>15</v>
+      </c>
+      <c r="F43" t="n">
+        <v>221</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7</v>
+      </c>
+      <c r="H43" t="n">
+        <v>5</v>
+      </c>
+      <c r="I43" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>降龙靴</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>13</v>
+      </c>
+      <c r="H44" t="n">
+        <v>5</v>
+      </c>
+      <c r="I44" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>百淬刃</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" t="n">
+        <v>29</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>6</v>
+      </c>
+      <c r="I45" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>百淬衣</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>442</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>6</v>
+      </c>
+      <c r="I46" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>百淬壶</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="n">
+        <v>15</v>
+      </c>
+      <c r="F47" t="n">
+        <v>221</v>
+      </c>
+      <c r="G47" t="n">
+        <v>7</v>
+      </c>
+      <c r="H47" t="n">
+        <v>6</v>
+      </c>
+      <c r="I47" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>百淬履</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>13</v>
+      </c>
+      <c r="H48" t="n">
+        <v>6</v>
+      </c>
+      <c r="I48" t="n">
         <v>100</v>
       </c>
     </row>
